--- a/consent_forms/037_procurement_intake_form--consent_forms.xlsx
+++ b/consent_forms/037_procurement_intake_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'direct_procurement',_'value':_'direct_procurement'}</t>
+          <t>direct_procurement</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'Direct Procurement', 'value': 'Direct_Procurement'}</t>
+          <t>Direct Procurement</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'indirect_procurement',_'value':_'indirect_procurement'}</t>
+          <t>indirect_procurement</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'Indirect Procurement', 'value': 'Indirect_Procurement'}</t>
+          <t>Indirect Procurement</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'electronic_bid',_'value':_'electronic_bid'}</t>
+          <t>electronic_bid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Electronic Bid', 'value': 'Electronic_Bid'}</t>
+          <t>Electronic Bid</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'physical_bid',_'value':_'physical_bid'}</t>
+          <t>physical_bid</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Physical Bid', 'value': 'Physical_Bid'}</t>
+          <t>Physical Bid</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'fixed-price_contract',_'value':_'fixed_price_contract'}</t>
+          <t>fixed_price_contract</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Fixed-Price Contract', 'value': 'Fixed_Price_Contract'}</t>
+          <t>Fixed Price Contract</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'cost-plus_contract',_'value':_'costplus_contract'}</t>
+          <t>costplus_contract</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'Cost-Plus Contract', 'value': 'CostPlus_Contract'}</t>
+          <t>CostPlus Contract</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'open_procurement',_'value':_'open_procurement'}</t>
+          <t>open_procurement</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'Open Procurement', 'value': 'Open_Procurement'}</t>
+          <t>Open Procurement</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'closed_procurement',_'value':_'closed_procurement'}</t>
+          <t>closed_procurement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'Closed Procurement', 'value': 'Closed_Procurement'}</t>
+          <t>Closed Procurement</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'internal',_'value':_'internal'}</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'Internal', 'value': 'Internal'}</t>
+          <t>Internal</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'external',_'value':_'external'}</t>
+          <t>external</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'External', 'value': 'External'}</t>
+          <t>External</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'Active', 'value': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'Cancelled', 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'vendor_1',_'value':_'vendor_1'}</t>
+          <t>vendor_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'Vendor 1', 'value': 'Vendor_1'}</t>
+          <t>Vendor 1</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'vendor_2',_'value':_'vendor_2'}</t>
+          <t>vendor_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'Vendor 2', 'value': 'Vendor_2'}</t>
+          <t>Vendor 2</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'vendor_3',_'value':_'vendor_3'}</t>
+          <t>vendor_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'Vendor 3', 'value': 'Vendor_3'}</t>
+          <t>Vendor 3</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': 'Email', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': 'Phone', 'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_'in-person',_'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': 'In-person', 'value': 'In_person'}</t>
+          <t>In person</t>
         </is>
       </c>
     </row>
